--- a/artfynd/A 45719-2021 artfynd.xlsx
+++ b/artfynd/A 45719-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45719-2021 artfynd.xlsx
+++ b/artfynd/A 45719-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2871,6 +2871,786 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130834065</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Siksjöbergsgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>516895</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6677512</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130834047</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91738</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Övra Starbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516932</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6677233</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130834071</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Siksjöbergsgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516848</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6677496</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130834063</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91738</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Siksjöbergsgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>516858</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6677494</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130834046</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Övra Starbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>516934</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6677235</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130834062</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Siksjöbergsgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>516859</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6677497</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130834054</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97842</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Övra Starbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>516969</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6677335</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130834060</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97845</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Övra Starbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>516909</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6677366</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45719-2021 artfynd.xlsx
+++ b/artfynd/A 45719-2021 artfynd.xlsx
@@ -2973,7 +2973,7 @@
         <v>130834047</v>
       </c>
       <c r="B21" t="n">
-        <v>91738</v>
+        <v>91739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3067,49 +3067,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130834071</v>
+        <v>130834063</v>
       </c>
       <c r="B22" t="n">
-        <v>57876</v>
+        <v>91739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100048</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siksjöbergsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516848</v>
+        <v>516858</v>
       </c>
       <c r="R22" t="n">
-        <v>6677496</v>
+        <v>6677494</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3168,45 +3164,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130834063</v>
+        <v>130834071</v>
       </c>
       <c r="B23" t="n">
-        <v>91738</v>
+        <v>57877</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100048</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siksjöbergsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516858</v>
+        <v>516848</v>
       </c>
       <c r="R23" t="n">
-        <v>6677494</v>
+        <v>6677496</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3268,7 +3268,7 @@
         <v>130834046</v>
       </c>
       <c r="B24" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130834054</v>
+        <v>130834060</v>
       </c>
       <c r="B26" t="n">
-        <v>97842</v>
+        <v>97848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516969</v>
+        <v>516909</v>
       </c>
       <c r="R26" t="n">
-        <v>6677335</v>
+        <v>6677366</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,7 +3556,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130834060</v>
+        <v>130834054</v>
       </c>
       <c r="B27" t="n">
         <v>97845</v>
@@ -3567,16 +3567,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>516909</v>
+        <v>516969</v>
       </c>
       <c r="R27" t="n">
-        <v>6677366</v>
+        <v>6677335</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 45719-2021 artfynd.xlsx
+++ b/artfynd/A 45719-2021 artfynd.xlsx
@@ -3067,45 +3067,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130834063</v>
+        <v>130834071</v>
       </c>
       <c r="B22" t="n">
-        <v>91739</v>
+        <v>57877</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100048</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siksjöbergsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516858</v>
+        <v>516848</v>
       </c>
       <c r="R22" t="n">
-        <v>6677494</v>
+        <v>6677496</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3164,49 +3168,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130834071</v>
+        <v>130834063</v>
       </c>
       <c r="B23" t="n">
-        <v>57877</v>
+        <v>91739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100048</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siksjöbergsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516848</v>
+        <v>516858</v>
       </c>
       <c r="R23" t="n">
-        <v>6677496</v>
+        <v>6677494</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130834060</v>
+        <v>130834054</v>
       </c>
       <c r="B26" t="n">
-        <v>97848</v>
+        <v>97845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516909</v>
+        <v>516969</v>
       </c>
       <c r="R26" t="n">
-        <v>6677366</v>
+        <v>6677335</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130834054</v>
+        <v>130834060</v>
       </c>
       <c r="B27" t="n">
-        <v>97845</v>
+        <v>97848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,16 +3567,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>516969</v>
+        <v>516909</v>
       </c>
       <c r="R27" t="n">
-        <v>6677335</v>
+        <v>6677366</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 45719-2021 artfynd.xlsx
+++ b/artfynd/A 45719-2021 artfynd.xlsx
@@ -3459,10 +3459,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130834054</v>
+        <v>130834060</v>
       </c>
       <c r="B26" t="n">
-        <v>97845</v>
+        <v>97848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516969</v>
+        <v>516909</v>
       </c>
       <c r="R26" t="n">
-        <v>6677335</v>
+        <v>6677366</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130834060</v>
+        <v>130834054</v>
       </c>
       <c r="B27" t="n">
-        <v>97848</v>
+        <v>97845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,16 +3567,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>516909</v>
+        <v>516969</v>
       </c>
       <c r="R27" t="n">
-        <v>6677366</v>
+        <v>6677335</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 45719-2021 artfynd.xlsx
+++ b/artfynd/A 45719-2021 artfynd.xlsx
@@ -2973,7 +2973,7 @@
         <v>130834047</v>
       </c>
       <c r="B21" t="n">
-        <v>91739</v>
+        <v>91747</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3067,49 +3067,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130834071</v>
+        <v>130834063</v>
       </c>
       <c r="B22" t="n">
-        <v>57877</v>
+        <v>91747</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100048</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siksjöbergsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516848</v>
+        <v>516858</v>
       </c>
       <c r="R22" t="n">
-        <v>6677496</v>
+        <v>6677494</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3168,45 +3164,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130834063</v>
+        <v>130834071</v>
       </c>
       <c r="B23" t="n">
-        <v>91739</v>
+        <v>57877</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100048</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siksjöbergsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516858</v>
+        <v>516848</v>
       </c>
       <c r="R23" t="n">
-        <v>6677494</v>
+        <v>6677496</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3268,7 +3268,7 @@
         <v>130834046</v>
       </c>
       <c r="B24" t="n">
-        <v>92498</v>
+        <v>92506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>130834060</v>
       </c>
       <c r="B26" t="n">
-        <v>97848</v>
+        <v>97857</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>130834054</v>
       </c>
       <c r="B27" t="n">
-        <v>97845</v>
+        <v>97854</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45719-2021 artfynd.xlsx
+++ b/artfynd/A 45719-2021 artfynd.xlsx
@@ -3067,45 +3067,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130834063</v>
+        <v>130834071</v>
       </c>
       <c r="B22" t="n">
-        <v>91747</v>
+        <v>57877</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100048</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siksjöbergsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516858</v>
+        <v>516848</v>
       </c>
       <c r="R22" t="n">
-        <v>6677494</v>
+        <v>6677496</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3164,49 +3168,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130834071</v>
+        <v>130834063</v>
       </c>
       <c r="B23" t="n">
-        <v>57877</v>
+        <v>91747</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100048</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siksjöbergsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516848</v>
+        <v>516858</v>
       </c>
       <c r="R23" t="n">
-        <v>6677496</v>
+        <v>6677494</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130834060</v>
+        <v>130834054</v>
       </c>
       <c r="B26" t="n">
-        <v>97857</v>
+        <v>97854</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516909</v>
+        <v>516969</v>
       </c>
       <c r="R26" t="n">
-        <v>6677366</v>
+        <v>6677335</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130834054</v>
+        <v>130834060</v>
       </c>
       <c r="B27" t="n">
-        <v>97854</v>
+        <v>97857</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,16 +3567,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>516969</v>
+        <v>516909</v>
       </c>
       <c r="R27" t="n">
-        <v>6677335</v>
+        <v>6677366</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 45719-2021 artfynd.xlsx
+++ b/artfynd/A 45719-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98289819</v>
+        <v>98289712</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516781.9761794442</v>
+        <v>516925</v>
       </c>
       <c r="R2" t="n">
-        <v>6677410.540129327</v>
+        <v>6677533</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,24 +747,14 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gnagspår   FLD0081 (Calluna AB) NVI</t>
+          <t>Mycket riklig på murken granlåga  FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,64 +774,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Josefina Pehrson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98289716</v>
+        <v>130834053</v>
       </c>
       <c r="B3" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2813</v>
+        <v>1067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.) R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+          <t>Övra Starbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516941.1666516176</v>
+        <v>516903</v>
       </c>
       <c r="R3" t="n">
-        <v>6677522.536262212</v>
+        <v>6677229</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,27 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>FLD0081 (Calluna AB) NVI</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,49 +866,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98289689</v>
+        <v>98289697</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516804.1114452771</v>
+        <v>516809</v>
       </c>
       <c r="R4" t="n">
-        <v>6677465.776451503</v>
+        <v>6677466</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,19 +950,9 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1038,42 +984,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98289777</v>
+        <v>98289796</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1082,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516991.4707314063</v>
+        <v>516814</v>
       </c>
       <c r="R5" t="n">
-        <v>6677510.8489863</v>
+        <v>6677511</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1112,27 +1053,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnagspår   FLD0081 (Calluna AB) NVI</t>
+          <t>FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,22 +1083,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Via Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98289796</v>
+        <v>130834048</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,24 +1118,20 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+          <t>Övra Starbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516814.3514476551</v>
+        <v>516895</v>
       </c>
       <c r="R6" t="n">
-        <v>6677511.023389624</v>
+        <v>6677241</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,27 +1155,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>FLD0081 (Calluna AB) NVI</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,69 +1175,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98289792</v>
+        <v>130834051</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+          <t>Övra Starbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516782.0309047377</v>
+        <v>516903</v>
       </c>
       <c r="R7" t="n">
-        <v>6677398.619269138</v>
+        <v>6677229</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,27 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>FLD0081 (Calluna AB) NVI</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,27 +1272,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98289707</v>
+        <v>130834050</v>
       </c>
       <c r="B8" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,41 +1295,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+          <t>Övra Starbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516858.647990866</v>
+        <v>516896</v>
       </c>
       <c r="R8" t="n">
-        <v>6677399.468513021</v>
+        <v>6677239</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,27 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lockläte   FLD0081 (Calluna AB) NVI</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,27 +1369,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98289712</v>
+        <v>130834052</v>
       </c>
       <c r="B9" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,41 +1392,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+          <t>Övra Starbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516925.1979863503</v>
+        <v>516902</v>
       </c>
       <c r="R9" t="n">
-        <v>6677532.892917851</v>
+        <v>6677228</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1596,27 +1446,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket riklig på murken granlåga  FLD0081 (Calluna AB) NVI</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,27 +1466,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98289729</v>
+        <v>98289716</v>
       </c>
       <c r="B10" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,26 +1489,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1687,10 +1517,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516881.4125011759</v>
+        <v>516942</v>
       </c>
       <c r="R10" t="n">
-        <v>6677533.683840181</v>
+        <v>6677522</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1717,22 +1547,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1764,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98289700</v>
+        <v>98289711</v>
       </c>
       <c r="B11" t="n">
-        <v>95572</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,26 +1595,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221063</v>
+        <v>2818</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1808,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516918.5211616535</v>
+        <v>516859</v>
       </c>
       <c r="R11" t="n">
-        <v>6677578.061049111</v>
+        <v>6677522</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1841,24 +1656,14 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>FLD0081 (Calluna AB) NVI</t>
+          <t>Sparsam på låga  FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,57 +1690,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98289706</v>
+        <v>130834046</v>
       </c>
       <c r="B12" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+          <t>Övra Starbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516952.9042234386</v>
+        <v>516934</v>
       </c>
       <c r="R12" t="n">
-        <v>6677566.299775328</v>
+        <v>6677235</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1959,27 +1755,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lockläte   FLD0081 (Calluna AB) NVI</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,49 +1775,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98289697</v>
+        <v>98289689</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2050,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516809.0866382779</v>
+        <v>516804</v>
       </c>
       <c r="R13" t="n">
-        <v>6677465.799325188</v>
+        <v>6677466</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2083,19 +1859,9 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2127,15 +1893,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98289788</v>
+        <v>98289792</v>
       </c>
       <c r="B14" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,26 +1904,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2171,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516791.4681242868</v>
+        <v>516782</v>
       </c>
       <c r="R14" t="n">
-        <v>6677510.421505215</v>
+        <v>6677399</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2204,24 +1965,14 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gnagspår FLD0081 (Calluna AB) NVI</t>
+          <t>FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,15 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>98289844</v>
+        <v>130834047</v>
       </c>
       <c r="B15" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,41 +2010,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+          <t>Övra Starbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516791.4681242868</v>
+        <v>516932</v>
       </c>
       <c r="R15" t="n">
-        <v>6677510.421505215</v>
+        <v>6677233</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2322,27 +2064,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gnagspår   FLD0081 (Calluna AB) NVI</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2357,27 +2084,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>98289806</v>
+        <v>130834063</v>
       </c>
       <c r="B16" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,41 +2107,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+          <t>Siksjöbergsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516814.4085636649</v>
+        <v>516858</v>
       </c>
       <c r="R16" t="n">
-        <v>6677498.606166115</v>
+        <v>6677494</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2443,27 +2161,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>FLD0081 (Calluna AB) NVI</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2478,27 +2181,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>98289711</v>
+        <v>130834043</v>
       </c>
       <c r="B17" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,41 +2204,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>6439</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+          <t>Övra Starbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516858.5843036982</v>
+        <v>517053</v>
       </c>
       <c r="R17" t="n">
-        <v>6677521.161076481</v>
+        <v>6677214</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2564,27 +2258,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sparsam på låga  FLD0081 (Calluna AB) NVI</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,27 +2278,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>108929108</v>
+        <v>130834045</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,53 +2301,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>6457</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Siksberget, Dlr</t>
+          <t>Övra Starbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517043.0083198285</v>
+        <v>517051</v>
       </c>
       <c r="R18" t="n">
-        <v>6677554.798152151</v>
+        <v>6677201</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2700,22 +2355,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-08-06</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2730,27 +2375,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>108929136</v>
+        <v>130834071</v>
       </c>
       <c r="B19" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2758,53 +2398,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205998</v>
+        <v>100048</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Siksberget, Dlr</t>
+          <t>Siksjöbergsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517043.0083198285</v>
+        <v>516848</v>
       </c>
       <c r="R19" t="n">
-        <v>6677554.798152151</v>
+        <v>6677496</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2831,22 +2456,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-08-06</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2861,22 +2476,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130834065</v>
+        <v>130834062</v>
       </c>
       <c r="B20" t="n">
-        <v>8440</v>
+        <v>4775</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2884,21 +2499,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2908,10 +2523,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516895</v>
+        <v>516859</v>
       </c>
       <c r="R20" t="n">
-        <v>6677512</v>
+        <v>6677497</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2970,10 +2585,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130834047</v>
+        <v>98289777</v>
       </c>
       <c r="B21" t="n">
-        <v>91772</v>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2981,37 +2596,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Övra Starbo, Dlr</t>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516932</v>
+        <v>516991</v>
       </c>
       <c r="R21" t="n">
-        <v>6677233</v>
+        <v>6677511</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3035,12 +2654,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2021-11-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gnagspår   FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,22 +2679,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130834063</v>
+        <v>98289844</v>
       </c>
       <c r="B22" t="n">
-        <v>91772</v>
+        <v>5179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,37 +2702,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Siksjöbergsgruvan, Dlr</t>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516858</v>
+        <v>516792</v>
       </c>
       <c r="R22" t="n">
-        <v>6677494</v>
+        <v>6677510</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3132,12 +2760,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gnagspår   FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3152,61 +2785,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Via Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130834071</v>
+        <v>130834044</v>
       </c>
       <c r="B23" t="n">
-        <v>57897</v>
+        <v>44177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100048</v>
+        <v>101735</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Siksjöbergsgruvan, Dlr</t>
+          <t>Övra Starbo, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516848</v>
+        <v>517052</v>
       </c>
       <c r="R23" t="n">
-        <v>6677496</v>
+        <v>6677214</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3233,12 +2862,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3265,48 +2894,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130834046</v>
+        <v>98289706</v>
       </c>
       <c r="B24" t="n">
-        <v>92531</v>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Övra Starbo, Dlr</t>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516934</v>
+        <v>516952</v>
       </c>
       <c r="R24" t="n">
-        <v>6677235</v>
+        <v>6677567</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3330,12 +2963,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Lockläte   FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3350,60 +2988,64 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130834062</v>
+        <v>98289707</v>
       </c>
       <c r="B25" t="n">
-        <v>4773</v>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Siksjöbergsgruvan, Dlr</t>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
         <v>516859</v>
       </c>
       <c r="R25" t="n">
-        <v>6677497</v>
+        <v>6677399</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3427,12 +3069,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Lockläte   FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3447,22 +3094,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130834060</v>
+        <v>98289788</v>
       </c>
       <c r="B26" t="n">
-        <v>97882</v>
+        <v>5199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,37 +3117,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221946</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Övra Starbo, Dlr</t>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516909</v>
+        <v>516792</v>
       </c>
       <c r="R26" t="n">
-        <v>6677366</v>
+        <v>6677510</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3524,12 +3175,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gnagspår FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,22 +3200,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Via Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130834054</v>
+        <v>98289819</v>
       </c>
       <c r="B27" t="n">
-        <v>97879</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,37 +3223,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Övra Starbo, Dlr</t>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>516969</v>
+        <v>516781</v>
       </c>
       <c r="R27" t="n">
-        <v>6677335</v>
+        <v>6677410</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3621,12 +3281,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gnagspår   FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3641,15 +3306,876 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Via Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130834065</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Siksjöbergsgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>516895</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6677512</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Tore Dahlberg</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Tore Dahlberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>108929108</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Siksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>517043</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6677555</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-08-06</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>108929136</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Siksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>517043</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6677555</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-08-06</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>98289700</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98030</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>516919</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6677578</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>FLD0081 (Calluna AB) NVI</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>98289729</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>516881</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6677533</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>FLD0081 (Calluna AB) NVI</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>98289806</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>516814</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6677499</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>FLD0081 (Calluna AB) NVI</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130834054</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Övra Starbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>516969</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6677335</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130834060</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Övra Starbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>516909</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6677366</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45719-2021 artfynd.xlsx
+++ b/artfynd/A 45719-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289712</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834053</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289697</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289796</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834048</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834051</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834050</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834052</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289716</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289711</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834046</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289689</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289792</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2093,6 +2163,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834047</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2190,6 +2265,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834063</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2287,6 +2367,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834043</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2384,6 +2469,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834045</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2485,6 +2575,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834071</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2582,6 +2677,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834062</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2688,6 +2788,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289777</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2794,6 +2899,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289844</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2891,6 +3001,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834044</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2997,6 +3112,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289706</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3103,6 +3223,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289707</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3209,6 +3334,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289788</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3315,6 +3445,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289819</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3412,6 +3547,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834065</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3538,6 +3678,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108929108</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3664,6 +3809,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108929136</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3770,6 +3920,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289700</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3876,6 +4031,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289729</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3982,6 +4142,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98289806</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4079,6 +4244,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834054</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4176,8 +4346,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834060</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>